--- a/basedatos_partidas/salida/descompuestos/07.05.02.110.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.05.02.110.xlsx
@@ -584,10 +584,10 @@
         <v>0.08</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="14">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>7.2</v>
+        <v>7.26</v>
       </c>
       <c r="H22" t="n">
         <v>0.07000000000000001</v>
@@ -788,7 +788,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>7.27</v>
+        <v>7.33</v>
       </c>
     </row>
   </sheetData>
